--- a/server/public/duty/duty-temp.xlsx
+++ b/server/public/duty/duty-temp.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
   <si>
     <t>工单类型</t>
   </si>
@@ -50,7 +50,7 @@
     <t>硬件</t>
   </si>
   <si>
-    <t>2026-02-13 12:00:00</t>
+    <t>2026-03-06 12:00</t>
   </si>
   <si>
     <t>测试硬件</t>
@@ -65,7 +65,7 @@
     <t>软件</t>
   </si>
   <si>
-    <t>2026-02-13 12:30:00</t>
+    <t>2026-03-06 12:30</t>
   </si>
   <si>
     <t>测试软件</t>
@@ -75,6 +75,45 @@
   </si>
   <si>
     <t>测试软件结果</t>
+  </si>
+  <si>
+    <t>自动</t>
+  </si>
+  <si>
+    <t>测试硬件2</t>
+  </si>
+  <si>
+    <t>测试硬件描述2</t>
+  </si>
+  <si>
+    <t>测试硬件结果2</t>
+  </si>
+  <si>
+    <t>测试软件2</t>
+  </si>
+  <si>
+    <t>测试软件描述2</t>
+  </si>
+  <si>
+    <t>测试软件结果2</t>
+  </si>
+  <si>
+    <t>2026-03-06 13:00</t>
+  </si>
+  <si>
+    <t>测试硬件3</t>
+  </si>
+  <si>
+    <t>测试硬件描述3</t>
+  </si>
+  <si>
+    <t>2026-03-06 13:30</t>
+  </si>
+  <si>
+    <t>测试软件3</t>
+  </si>
+  <si>
+    <t>测试软件描述3</t>
   </si>
   <si>
     <t>遗留</t>
@@ -1228,8 +1267,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="18.4326923076923" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.3365384615385" customWidth="1"/>
@@ -1294,10 +1333,78 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
+      <c r="C4" t="s">
         <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
